--- a/public/assets/BOs/Nuwa.xlsx
+++ b/public/assets/BOs/Nuwa.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33040DB1-017A-4B39-9A95-519AD5F5591E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260304FC-655A-4B3D-B257-F79A3DB1E1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil3" sheetId="5" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="3" r:id="rId2"/>
-    <sheet name="Feuil2" sheetId="4" r:id="rId3"/>
+    <sheet name="Feuil5" sheetId="7" r:id="rId1"/>
+    <sheet name="Feuil4" sheetId="6" r:id="rId2"/>
+    <sheet name="Feuil3" sheetId="5" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="3" r:id="rId4"/>
+    <sheet name="Feuil2" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
   <si>
     <t>Archaic</t>
   </si>
@@ -668,12 +670,496 @@
   <si>
     <t>Standard Build Order - By BqvH</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>1 Peasant builds a Silo then goes on Food
+1 Peasant makes a Silo then goes on Gold
+Kuafu makes a House, a Silo then goes on Wood</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/ 1 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>7 Peasants on Food</t>
+  </si>
+  <si>
+    <t>Once you have 150 wood move Kuafu to Gold (build Silo)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Kuafu on Wood</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Kuafu builds Temple when you have 150 Gold</t>
+  </si>
+  <si>
+    <t>Advance (3:18)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 3 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Redistrubite peasants to wood and gold based on gameplan</t>
+  </si>
+  <si>
+    <t>Classical (4:18)</t>
+  </si>
+  <si>
+    <t>Chinese - 4:18 tripple Kuafu - By Mirez</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>2 Peasant builds a Silo then go on Food
+Kuafu makes a Silo then goes on Wood</t>
+  </si>
+  <si>
+    <t>auto build a House &amp; Gold Silo on favoured land</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/ 1 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/ 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Once you have 150 wood move Kuafu to Gold</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/ 0 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Chieftain Gold</t>
+  </si>
+  <si>
+    <t>Advance (2:42)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Classical (3:42)</t>
+  </si>
+  <si>
+    <t>3:56 early Chieftain build - By Mirez</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -753,8 +1239,57 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -789,6 +1324,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -857,7 +1398,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -870,6 +1411,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -888,22 +1462,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1244,149 +1802,440 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5EBA25-327C-47A4-B99A-6D43E7CDFA38}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75">
+      <c r="A1" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7C7491-D2D0-4C75-B939-6585522EDD01}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75">
+      <c r="A1" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="16"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="10"/>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="10"/>
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="12"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A16:D16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C11CC5-D1D1-4007-B2F9-7DD23D073ABF}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" ht="19.5">
+      <c r="A1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:4" ht="21">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:4" ht="17.25">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13" t="s">
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="11"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="11"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:4" ht="17.25">
+      <c r="A9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" ht="17.25">
+      <c r="A11" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="13" t="s">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="13" t="s">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5"/>
+      <c r="B15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1399,28 +2248,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A134E6A9-645D-47EA-9AC6-7BF90D1A3CB1}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" ht="18.75" thickBot="1">
+      <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="44.25" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1428,7 +2277,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="139.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="158.25" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -1440,7 +2289,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="72.75" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -1454,7 +2303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="30" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1464,15 +2313,15 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4" ht="44.25" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -1480,7 +2329,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="111.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="115.5" thickBot="1">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -1490,15 +2339,15 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" ht="44.25" thickBot="1">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1506,7 +2355,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="72.75" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -1518,7 +2367,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="58.5" thickBot="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -1541,28 +2390,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A1AAA0-9F3F-488F-B5A6-6B93208C627A}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" ht="18.75" thickBot="1">
+      <c r="A1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="44.25" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1570,7 +2419,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="84" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="101.25" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1584,7 +2433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="58.5" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1596,7 +2445,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="30" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -1606,7 +2455,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="72.75" thickBot="1">
       <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
@@ -1618,7 +2467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="72.75" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -1632,7 +2481,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="72.75" thickBot="1">
       <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
@@ -1644,15 +2493,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A10" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" ht="44.25" thickBot="1">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1660,7 +2509,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="58.5" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
@@ -1672,15 +2521,15 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A13" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+    </row>
+    <row r="14" spans="1:4" ht="44.25" thickBot="1">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -1688,7 +2537,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="58.5" thickBot="1">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>

--- a/public/assets/BOs/Nuwa.xlsx
+++ b/public/assets/BOs/Nuwa.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\Deities of Death\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33040DB1-017A-4B39-9A95-519AD5F5591E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD11AA6-D3F4-4081-B709-156E466453C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil3" sheetId="5" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="3" r:id="rId2"/>
-    <sheet name="Feuil2" sheetId="4" r:id="rId3"/>
+    <sheet name="Feuil5" sheetId="7" r:id="rId1"/>
+    <sheet name="Feuil4" sheetId="6" r:id="rId2"/>
+    <sheet name="Feuil3" sheetId="5" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="3" r:id="rId4"/>
+    <sheet name="Feuil2" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>Archaic</t>
   </si>
@@ -668,12 +670,476 @@
   <si>
     <t>Standard Build Order - By BqvH</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>1 Peasant builds a Silo then goes on Food
+1 Peasant makes a Silo then goes on Gold
+Kuafu makes a House, a Silo then goes on Wood</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/ 1 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>7 Peasants on Food</t>
+  </si>
+  <si>
+    <t>Once you have 150 wood move Kuafu to Gold (build Silo)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Kuafu on Wood</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Kuafu builds Temple when you have 150 Gold</t>
+  </si>
+  <si>
+    <t>Advance (3:18)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 3 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Redistrubite peasants to wood and gold based on gameplan</t>
+  </si>
+  <si>
+    <t>Classical (4:18)</t>
+  </si>
+  <si>
+    <t>Chinese - 4:18 tripple Kuafu - By Mirez</t>
+  </si>
+  <si>
+    <t>2 Peasant builds a Silo then go on Food
+Kuafu makes a Silo then goes on Wood</t>
+  </si>
+  <si>
+    <t>auto build a House &amp; Gold Silo on favoured land</t>
+  </si>
+  <si>
+    <t>Once you have 150 wood move Kuafu to Gold</t>
+  </si>
+  <si>
+    <t>Nuwa - 3:46 early Chieftain V2 build - Mirez</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ 1 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Chieftain Wood</t>
+  </si>
+  <si>
+    <t>Advance (2:46)</t>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Classical (3:46)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -753,8 +1219,57 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -789,6 +1304,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -857,7 +1378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -870,6 +1391,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -888,22 +1442,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1244,149 +1782,445 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5EBA25-327C-47A4-B99A-6D43E7CDFA38}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="38.58203125" defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5" thickBot="1">
+      <c r="A1" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" thickBot="1">
+      <c r="A2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="16" thickBot="1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="29" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="16" thickBot="1">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="16" thickBot="1">
+      <c r="A6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="16" thickBot="1">
+      <c r="A7" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4" ht="16" thickBot="1">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="29" thickBot="1">
+      <c r="A9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="16" thickBot="1">
+      <c r="A10" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" ht="16" thickBot="1">
+      <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7C7491-D2D0-4C75-B939-6585522EDD01}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5">
+      <c r="A1" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="16"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="10"/>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="10"/>
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="12"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A16:D16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C11CC5-D1D1-4007-B2F9-7DD23D073ABF}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" ht="19.5">
+      <c r="A1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:4" ht="21">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:4" ht="17">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13" t="s">
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="11"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="11"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:4" ht="17">
+      <c r="A9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" ht="17">
+      <c r="A11" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="13" t="s">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="13" t="s">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5"/>
+      <c r="B15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1399,28 +2233,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A134E6A9-645D-47EA-9AC6-7BF90D1A3CB1}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" ht="18.5" thickBot="1">
+      <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" thickBot="1">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="57" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1428,7 +2262,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="139.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="155" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -1440,7 +2274,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="71" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -1454,7 +2288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1464,15 +2298,15 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:4" ht="16" thickBot="1">
+      <c r="A7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4" ht="57" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -1480,7 +2314,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="111.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="113" thickBot="1">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -1490,15 +2324,15 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:4" ht="16" thickBot="1">
+      <c r="A10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" ht="57" thickBot="1">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1506,7 +2340,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="71" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -1518,7 +2352,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="57" thickBot="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -1541,28 +2375,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A1AAA0-9F3F-488F-B5A6-6B93208C627A}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" ht="18.5" thickBot="1">
+      <c r="A1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" thickBot="1">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="57" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1570,7 +2404,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="84" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="99" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1584,7 +2418,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="57" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1596,7 +2430,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -1606,7 +2440,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="71" thickBot="1">
       <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
@@ -1618,7 +2452,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="71" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -1632,7 +2466,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="71" thickBot="1">
       <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
@@ -1644,15 +2478,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:4" ht="16" thickBot="1">
+      <c r="A10" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" ht="57" thickBot="1">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1660,7 +2494,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="57" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
@@ -1672,15 +2506,15 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:4" ht="16" thickBot="1">
+      <c r="A13" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" spans="1:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+    </row>
+    <row r="14" spans="1:4" ht="57" thickBot="1">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -1688,7 +2522,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="57" thickBot="1">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
